--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -227,22 +227,22 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
   </si>
   <si>
     <t>NC</t>
@@ -1091,22 +1091,22 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1142,10 +1142,10 @@
         <v>7</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE4">
         <v>7</v>
@@ -1192,22 +1192,22 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1240,13 +1240,13 @@
         <v>6</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>6</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>7</v>
@@ -1255,7 +1255,7 @@
         <v>7</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1293,22 +1293,22 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1353,10 +1353,10 @@
         <v>7</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1394,22 +1394,22 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE7">
         <v>7</v>
@@ -1457,7 +1457,7 @@
         <v>6</v>
       </c>
       <c r="AG7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1495,22 +1495,22 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1543,7 +1543,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1596,22 +1596,22 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1644,19 +1644,19 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9">
         <v>6</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1697,22 +1697,22 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1745,13 +1745,13 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10">
         <v>6</v>
@@ -1798,22 +1798,22 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1861,7 +1861,7 @@
         <v>5</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1899,22 +1899,22 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1953,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE12">
         <v>8</v>
@@ -2000,22 +2000,22 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -2048,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -2101,22 +2101,22 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -2152,10 +2152,10 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14">
         <v>6</v>
@@ -2202,22 +2202,22 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2262,7 +2262,7 @@
         <v>6</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2303,22 +2303,22 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2354,10 +2354,10 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE16">
         <v>7</v>
@@ -2404,22 +2404,22 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2455,10 +2455,10 @@
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE17">
         <v>9</v>
@@ -2505,22 +2505,22 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2553,19 +2553,19 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE18">
         <v>7</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2606,22 +2606,22 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2657,7 +2657,7 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD19">
         <v>7</v>
@@ -2707,22 +2707,22 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="AF20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -2808,22 +2808,22 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2859,10 +2859,10 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE21">
         <v>7</v>
@@ -2909,22 +2909,22 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2960,10 +2960,10 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE22">
         <v>6</v>
@@ -2972,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="AG22">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:33">
@@ -3010,22 +3010,22 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -3058,11 +3058,11 @@
         <v>7</v>
       </c>
       <c r="AB23">
+        <v>9</v>
+      </c>
+      <c r="AC23">
         <v>8</v>
       </c>
-      <c r="AC23">
-        <v>6</v>
-      </c>
       <c r="AD23">
         <v>6</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>5</v>
       </c>
       <c r="AF23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -3111,22 +3111,22 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -3159,13 +3159,13 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>9</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24">
         <v>6</v>
@@ -3174,7 +3174,7 @@
         <v>7</v>
       </c>
       <c r="AG24">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:33">
@@ -3212,22 +3212,22 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3263,16 +3263,16 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE25">
         <v>6</v>
       </c>
       <c r="AF25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3313,22 +3313,22 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3361,10 +3361,10 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD26">
         <v>7</v>
@@ -3414,22 +3414,22 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE27">
         <v>7</v>
@@ -3515,22 +3515,22 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3616,22 +3616,22 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3664,13 +3664,13 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>6</v>
       </c>
       <c r="AD29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE29">
         <v>6</v>
@@ -3679,7 +3679,7 @@
         <v>7</v>
       </c>
       <c r="AG29">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:33">
@@ -3717,22 +3717,22 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD30">
         <v>6</v>
@@ -3777,7 +3777,7 @@
         <v>5</v>
       </c>
       <c r="AF30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3818,22 +3818,22 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3866,13 +3866,13 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31">
         <v>6</v>
@@ -3919,22 +3919,22 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3967,19 +3967,19 @@
         <v>6</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE32">
         <v>6</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -4020,22 +4020,22 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -4083,7 +4083,7 @@
         <v>5</v>
       </c>
       <c r="AG33">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:33">
@@ -4121,22 +4121,22 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -4169,13 +4169,13 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC34">
         <v>10</v>
       </c>
       <c r="AD34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE34">
         <v>7</v>
@@ -4222,22 +4222,22 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4273,16 +4273,16 @@
         <v>5</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE35">
         <v>6</v>
       </c>
       <c r="AF35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4323,22 +4323,22 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4371,10 +4371,10 @@
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD36">
         <v>6</v>
@@ -4424,22 +4424,22 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4475,10 +4475,10 @@
         <v>5</v>
       </c>
       <c r="AC37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE37">
         <v>6</v>
@@ -4525,22 +4525,22 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4573,13 +4573,13 @@
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC38">
         <v>10</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE38">
         <v>6</v>
@@ -4588,7 +4588,7 @@
         <v>8</v>
       </c>
       <c r="AG38">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:33">
@@ -4626,22 +4626,22 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4674,13 +4674,13 @@
         <v>5</v>
       </c>
       <c r="AB39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE39">
         <v>6</v>
@@ -4689,7 +4689,7 @@
         <v>7</v>
       </c>
       <c r="AG39">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -4727,22 +4727,22 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4775,10 +4775,10 @@
         <v>6</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD40">
         <v>6</v>
@@ -4828,22 +4828,22 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -4876,10 +4876,10 @@
         <v>6</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD41">
         <v>7</v>
@@ -4929,22 +4929,22 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O42">
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -4977,19 +4977,19 @@
         <v>6</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>10</v>
       </c>
       <c r="AD42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE42">
         <v>6</v>
       </c>
       <c r="AF42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -5030,22 +5030,22 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O43">
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -5078,13 +5078,13 @@
         <v>6</v>
       </c>
       <c r="AB43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE43">
         <v>7</v>
@@ -5131,22 +5131,22 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O44">
         <v>-1</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
         <v>-1</v>
@@ -5185,7 +5185,7 @@
         <v>10</v>
       </c>
       <c r="AD44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE44">
         <v>6</v>
@@ -5378,7 +5378,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -5402,7 +5402,7 @@
         <v>100</v>
       </c>
       <c r="X4">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -5443,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -5455,7 +5455,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -5467,7 +5467,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -5479,7 +5479,7 @@
         <v>100</v>
       </c>
       <c r="X5">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -5597,7 +5597,7 @@
         <v>80</v>
       </c>
       <c r="L7">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -5609,7 +5609,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -5621,7 +5621,7 @@
         <v>80</v>
       </c>
       <c r="T7">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -5633,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -5674,19 +5674,19 @@
         <v>93.3</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -5698,19 +5698,19 @@
         <v>93.3</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U8">
         <v>100</v>
       </c>
       <c r="V8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="W8">
         <v>100</v>
       </c>
       <c r="X8">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -5763,7 +5763,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -5787,7 +5787,7 @@
         <v>100</v>
       </c>
       <c r="X9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -5828,7 +5828,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -5840,7 +5840,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -5852,7 +5852,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -5864,7 +5864,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -5911,16 +5911,16 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>38.6</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -5935,16 +5935,16 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="W11">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>85</v>
+        <v>38.6</v>
       </c>
       <c r="Y11">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -6148,7 +6148,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -6172,7 +6172,7 @@
         <v>100</v>
       </c>
       <c r="X14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -6225,7 +6225,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -6249,7 +6249,7 @@
         <v>100</v>
       </c>
       <c r="X15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -6302,7 +6302,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -6326,7 +6326,7 @@
         <v>100</v>
       </c>
       <c r="X16">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -6444,7 +6444,7 @@
         <v>86.7</v>
       </c>
       <c r="L18">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -6456,7 +6456,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -6468,7 +6468,7 @@
         <v>86.7</v>
       </c>
       <c r="T18">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6480,7 +6480,7 @@
         <v>100</v>
       </c>
       <c r="X18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -6610,7 +6610,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -6634,7 +6634,7 @@
         <v>100</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -6675,7 +6675,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -6699,7 +6699,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -6764,7 +6764,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -6788,7 +6788,7 @@
         <v>100</v>
       </c>
       <c r="X22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -6841,7 +6841,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -6865,7 +6865,7 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -6995,7 +6995,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -7019,7 +7019,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -7214,19 +7214,19 @@
         <v>80</v>
       </c>
       <c r="L28">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="M28">
         <v>100</v>
       </c>
       <c r="N28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -7238,19 +7238,19 @@
         <v>80</v>
       </c>
       <c r="T28">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="U28">
         <v>100</v>
       </c>
       <c r="V28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W28">
         <v>100</v>
       </c>
       <c r="X28">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -7297,13 +7297,13 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -7321,13 +7321,13 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="W29">
         <v>100</v>
       </c>
       <c r="X29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -7380,7 +7380,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -7404,7 +7404,7 @@
         <v>100</v>
       </c>
       <c r="X30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y30">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -7457,7 +7457,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -7469,7 +7469,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7481,7 +7481,7 @@
         <v>100</v>
       </c>
       <c r="X31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y31">
         <v>100</v>
@@ -7599,7 +7599,7 @@
         <v>86.7</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -7611,7 +7611,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -7623,7 +7623,7 @@
         <v>86.7</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="X33">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y33">
         <v>100</v>
@@ -7753,7 +7753,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -7765,7 +7765,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -7777,7 +7777,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -7789,7 +7789,7 @@
         <v>100</v>
       </c>
       <c r="X35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y35">
         <v>100</v>
@@ -7830,7 +7830,7 @@
         <v>80</v>
       </c>
       <c r="L36">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -7842,7 +7842,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -7854,7 +7854,7 @@
         <v>80</v>
       </c>
       <c r="T36">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -7866,7 +7866,7 @@
         <v>100</v>
       </c>
       <c r="X36">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -7907,7 +7907,7 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -7919,7 +7919,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -7931,7 +7931,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -7943,7 +7943,7 @@
         <v>100</v>
       </c>
       <c r="X37">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y37">
         <v>100</v>
@@ -7996,7 +7996,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -8020,7 +8020,7 @@
         <v>100</v>
       </c>
       <c r="X38">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Y38">
         <v>100</v>
@@ -8061,7 +8061,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -8073,7 +8073,7 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -8085,7 +8085,7 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U39">
         <v>100</v>
@@ -8097,7 +8097,7 @@
         <v>100</v>
       </c>
       <c r="X39">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y39">
         <v>100</v>
@@ -8138,7 +8138,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M40">
         <v>100</v>
@@ -8150,7 +8150,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -8162,7 +8162,7 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U40">
         <v>100</v>
@@ -8174,7 +8174,7 @@
         <v>100</v>
       </c>
       <c r="X40">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y40">
         <v>100</v>
@@ -8292,7 +8292,7 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M42">
         <v>100</v>
@@ -8316,7 +8316,7 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U42">
         <v>100</v>
@@ -8381,7 +8381,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Q43">
         <v>100</v>
@@ -8405,7 +8405,7 @@
         <v>100</v>
       </c>
       <c r="X43">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Y43">
         <v>100</v>
@@ -8603,7 +8603,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -8612,19 +8612,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>70.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>29.3</v>
+        <v>24.4</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8635,7 +8635,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -8656,7 +8656,7 @@
         <v>22</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8688,7 +8688,7 @@
         <v>17.1</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8708,19 +8708,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>85.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="G7" s="2">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8763,7 +8763,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
@@ -8772,19 +8772,19 @@
         <v>41</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9654,7 +9654,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9686,16 +9686,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920111</v>
+        <v>24330051920063</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -9709,22 +9709,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920111</v>
+        <v>24330051920063</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -9732,16 +9732,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920314</v>
+        <v>24330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -9755,22 +9755,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920314</v>
+        <v>24330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -9778,16 +9778,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920071</v>
+        <v>24330051920334</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -9801,16 +9801,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920071</v>
+        <v>24330051920334</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -9824,16 +9824,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920084</v>
+        <v>24330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -9847,22 +9847,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920084</v>
+        <v>24330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -9870,16 +9870,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920070</v>
+        <v>24330051920111</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -9893,39 +9893,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920063</v>
+        <v>24330051920111</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920337</v>
+        <v>24330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -9939,39 +9939,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920074</v>
+        <v>24330051920062</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920077</v>
+        <v>24330051920314</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -9985,39 +9985,39 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920067</v>
+        <v>24330051920314</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920082</v>
+        <v>24330051920068</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -10031,39 +10031,39 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920268</v>
+        <v>24330051920068</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920080</v>
+        <v>24330051920070</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -10077,16 +10077,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920339</v>
+        <v>24330051920074</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -10100,16 +10100,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920064</v>
+        <v>24330051920077</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -10123,16 +10123,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920069</v>
+        <v>24330051920067</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
@@ -10146,16 +10146,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920066</v>
+        <v>24330051920082</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -10169,16 +10169,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920109</v>
+        <v>24330051920268</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -10192,16 +10192,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920076</v>
+        <v>24330051920080</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -10215,16 +10215,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920062</v>
+        <v>24330051920339</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -10238,16 +10238,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920034</v>
+        <v>24330051920064</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -10261,16 +10261,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920079</v>
+        <v>24330051920069</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -10284,16 +10284,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920083</v>
+        <v>24330051920036</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -10307,16 +10307,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920068</v>
+        <v>24330051920066</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -10330,16 +10330,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920081</v>
+        <v>24330051920076</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -10353,16 +10353,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920075</v>
+        <v>24330051920034</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
@@ -10376,16 +10376,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920078</v>
+        <v>24330051920079</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
@@ -10394,6 +10394,144 @@
         <v>67</v>
       </c>
       <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920083</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>24330051920084</v>
+      </c>
+      <c r="B34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>67</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>24330051920081</v>
+      </c>
+      <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>24330051920075</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>67</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>24330051920072</v>
+      </c>
+      <c r="B37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>24330051920078</v>
+      </c>
+      <c r="B38" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -236,10 +236,10 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>González Sánchez Rene Aurelio</t>
@@ -1088,7 +1088,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -1100,7 +1100,7 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -1136,7 +1136,7 @@
         <v>-1</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>7</v>
@@ -1148,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="AE4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF4">
         <v>8</v>
@@ -1189,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -1237,7 +1237,7 @@
         <v>-1</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>8</v>
@@ -1249,7 +1249,7 @@
         <v>7</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF5">
         <v>7</v>
@@ -1290,7 +1290,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1302,7 +1302,7 @@
         <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -1338,7 +1338,7 @@
         <v>-1</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1391,7 +1391,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1403,7 +1403,7 @@
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -1451,7 +1451,7 @@
         <v>7</v>
       </c>
       <c r="AE7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF7">
         <v>6</v>
@@ -1492,7 +1492,7 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -1504,7 +1504,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -1593,7 +1593,7 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>7</v>
@@ -1641,7 +1641,7 @@
         <v>-1</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1694,7 +1694,7 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -1706,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>7</v>
@@ -1742,7 +1742,7 @@
         <v>-1</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -1754,7 +1754,7 @@
         <v>7</v>
       </c>
       <c r="AE10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF10">
         <v>8</v>
@@ -1795,7 +1795,7 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -1896,7 +1896,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>8</v>
@@ -1908,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -2009,7 +2009,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -2045,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -2057,7 +2057,7 @@
         <v>8</v>
       </c>
       <c r="AE13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF13">
         <v>10</v>
@@ -2098,7 +2098,7 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -2110,7 +2110,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -2211,7 +2211,7 @@
         <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>9</v>
@@ -2259,7 +2259,7 @@
         <v>7</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF15">
         <v>8</v>
@@ -2300,7 +2300,7 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -2312,7 +2312,7 @@
         <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>8</v>
@@ -2401,7 +2401,7 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2413,7 +2413,7 @@
         <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2461,7 +2461,7 @@
         <v>7</v>
       </c>
       <c r="AE17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF17">
         <v>8</v>
@@ -2502,7 +2502,7 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>8</v>
@@ -2514,7 +2514,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>7</v>
@@ -2550,7 +2550,7 @@
         <v>-1</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>8</v>
@@ -2603,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2615,7 +2615,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>9</v>
@@ -2651,7 +2651,7 @@
         <v>-1</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>9</v>
@@ -2663,7 +2663,7 @@
         <v>7</v>
       </c>
       <c r="AE19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF19">
         <v>10</v>
@@ -2704,7 +2704,7 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2716,7 +2716,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>5</v>
@@ -2764,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF20">
         <v>6</v>
@@ -2805,7 +2805,7 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2817,7 +2817,7 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -2906,7 +2906,7 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2918,7 +2918,7 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -3007,7 +3007,7 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -3019,7 +3019,7 @@
         <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>8</v>
@@ -3108,7 +3108,7 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -3120,7 +3120,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>7</v>
@@ -3156,7 +3156,7 @@
         <v>-1</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -3168,7 +3168,7 @@
         <v>7</v>
       </c>
       <c r="AE24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>7</v>
@@ -3209,7 +3209,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>7</v>
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -3257,7 +3257,7 @@
         <v>-1</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>7</v>
@@ -3269,7 +3269,7 @@
         <v>8</v>
       </c>
       <c r="AE25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF25">
         <v>8</v>
@@ -3310,7 +3310,7 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -3322,7 +3322,7 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -3370,7 +3370,7 @@
         <v>7</v>
       </c>
       <c r="AE26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26">
         <v>6</v>
@@ -3411,7 +3411,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -3423,7 +3423,7 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>9</v>
@@ -3471,7 +3471,7 @@
         <v>8</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF27">
         <v>10</v>
@@ -3512,7 +3512,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -3524,7 +3524,7 @@
         <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>5</v>
@@ -3613,7 +3613,7 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -3625,7 +3625,7 @@
         <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -3714,7 +3714,7 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -3726,7 +3726,7 @@
         <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>8</v>
@@ -3815,7 +3815,7 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -3875,7 +3875,7 @@
         <v>7</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF31">
         <v>8</v>
@@ -3916,7 +3916,7 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>9</v>
@@ -3964,7 +3964,7 @@
         <v>-1</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>8</v>
@@ -3976,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="AE32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF32">
         <v>8</v>
@@ -4017,7 +4017,7 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -4029,7 +4029,7 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>5</v>
@@ -4077,7 +4077,7 @@
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF33">
         <v>5</v>
@@ -4118,7 +4118,7 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -4130,7 +4130,7 @@
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>10</v>
@@ -4166,7 +4166,7 @@
         <v>-1</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>8</v>
@@ -4178,7 +4178,7 @@
         <v>8</v>
       </c>
       <c r="AE34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF34">
         <v>10</v>
@@ -4219,7 +4219,7 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -4231,7 +4231,7 @@
         <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>6</v>
@@ -4320,7 +4320,7 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -4332,7 +4332,7 @@
         <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>7</v>
@@ -4368,7 +4368,7 @@
         <v>-1</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>7</v>
@@ -4421,7 +4421,7 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>6</v>
@@ -4433,7 +4433,7 @@
         <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -4469,7 +4469,7 @@
         <v>-1</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB37">
         <v>5</v>
@@ -4522,7 +4522,7 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>7</v>
@@ -4534,7 +4534,7 @@
         <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
         <v>7</v>
@@ -4582,7 +4582,7 @@
         <v>7</v>
       </c>
       <c r="AE38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF38">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -4635,7 +4635,7 @@
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
         <v>6</v>
@@ -4724,7 +4724,7 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
         <v>9</v>
@@ -4736,7 +4736,7 @@
         <v>6</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>9</v>
@@ -4825,7 +4825,7 @@
         <v>-1</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
         <v>9</v>
@@ -4837,7 +4837,7 @@
         <v>7</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
         <v>10</v>
@@ -4873,7 +4873,7 @@
         <v>-1</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB41">
         <v>9</v>
@@ -4885,7 +4885,7 @@
         <v>7</v>
       </c>
       <c r="AE41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF41">
         <v>10</v>
@@ -4926,7 +4926,7 @@
         <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -4938,7 +4938,7 @@
         <v>8</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
         <v>10</v>
@@ -4974,7 +4974,7 @@
         <v>-1</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB42">
         <v>8</v>
@@ -4986,7 +4986,7 @@
         <v>8</v>
       </c>
       <c r="AE42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF42">
         <v>10</v>
@@ -5027,7 +5027,7 @@
         <v>-1</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
         <v>8</v>
@@ -5039,7 +5039,7 @@
         <v>9</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>6</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="AA43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB43">
         <v>7</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
         <v>9</v>
@@ -5140,7 +5140,7 @@
         <v>8</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P44">
         <v>9</v>
@@ -5176,7 +5176,7 @@
         <v>-1</v>
       </c>
       <c r="AA44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB44">
         <v>10</v>
@@ -5188,7 +5188,7 @@
         <v>7</v>
       </c>
       <c r="AE44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF44">
         <v>9</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="L7">
         <v>86.40000000000001</v>
@@ -5618,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="T7">
         <v>86.40000000000001</v>
@@ -5671,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="L8">
         <v>90.90000000000001</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="T8">
         <v>90.90000000000001</v>
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -5772,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L10">
         <v>95.5</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T10">
         <v>95.5</v>
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -5926,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -6157,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -6287,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -6441,7 +6441,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L18">
         <v>95.5</v>
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T18">
         <v>95.5</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -6749,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -6773,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -7312,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="L33">
         <v>95.5</v>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="T33">
         <v>95.5</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="L36">
         <v>90.90000000000001</v>
@@ -7851,7 +7851,7 @@
         <v>0</v>
       </c>
       <c r="S36">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="T36">
         <v>90.90000000000001</v>
@@ -8058,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L39">
         <v>95.5</v>
@@ -8082,7 +8082,7 @@
         <v>0</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T39">
         <v>95.5</v>
@@ -8580,19 +8580,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>70.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>29.3</v>
+        <v>24.4</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -8708,19 +8708,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>87.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>12.2</v>
+        <v>14.6</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8731,7 +8731,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
@@ -8752,7 +8752,7 @@
         <v>12.2</v>
       </c>
       <c r="H8">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9654,7 +9654,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9908,7 +9908,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -10054,16 +10054,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920070</v>
+        <v>24330051920299</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -10077,39 +10077,39 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920074</v>
+        <v>24330051920299</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920077</v>
+        <v>24330051920070</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -10123,16 +10123,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920067</v>
+        <v>24330051920074</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
@@ -10146,16 +10146,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920082</v>
+        <v>24330051920077</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -10169,16 +10169,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920268</v>
+        <v>24330051920067</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -10192,16 +10192,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920080</v>
+        <v>24330051920082</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -10215,16 +10215,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920339</v>
+        <v>24330051920268</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -10238,16 +10238,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920064</v>
+        <v>24330051920080</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -10261,16 +10261,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920069</v>
+        <v>24330051920339</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -10284,16 +10284,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920036</v>
+        <v>24330051920064</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -10307,16 +10307,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920066</v>
+        <v>24330051920069</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -10330,16 +10330,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920076</v>
+        <v>24330051920036</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -10353,16 +10353,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920034</v>
+        <v>24330051920066</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
@@ -10376,16 +10376,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920079</v>
+        <v>24330051920076</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
@@ -10399,16 +10399,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920083</v>
+        <v>24330051920034</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
@@ -10422,16 +10422,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920084</v>
+        <v>24330051920079</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -10445,16 +10445,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920081</v>
+        <v>24330051920083</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
@@ -10468,16 +10468,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920075</v>
+        <v>24330051920084</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
         <v>5</v>
@@ -10491,16 +10491,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920072</v>
+        <v>24330051920081</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E37" t="s">
         <v>5</v>
@@ -10514,16 +10514,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920078</v>
+        <v>24330051920075</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
@@ -10532,6 +10532,52 @@
         <v>67</v>
       </c>
       <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>24330051920072</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>24330051920078</v>
+      </c>
+      <c r="B40" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>67</v>
+      </c>
+      <c r="G40">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -221,30 +221,30 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -257,7 +257,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALJAVID</t>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -266,141 +269,42 @@
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PAYAN</t>
-  </si>
-  <si>
-    <t>PARADA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>RASCON</t>
   </si>
   <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
     <t>ISLAS</t>
   </si>
   <si>
     <t>TRONCO</t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>CHICUELLAR</t>
-  </si>
-  <si>
     <t>VALENTE</t>
   </si>
   <si>
@@ -410,16 +314,10 @@
     <t>AJACTLE</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
+    <t>VERONICA ITZEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN YAIR</t>
   </si>
   <si>
     <t>URIEL</t>
@@ -428,54 +326,6 @@
     <t>VICTOR ALEXIS</t>
   </si>
   <si>
-    <t>VERONICA ITZEL</t>
-  </si>
-  <si>
-    <t>HELI SAMUEL</t>
-  </si>
-  <si>
-    <t>ANGEL ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR RENE</t>
-  </si>
-  <si>
-    <t>ROBERTO OSVALDO</t>
-  </si>
-  <si>
-    <t>JAZMIN ISABEL</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>CHRISTIAN</t>
-  </si>
-  <si>
-    <t>CARLOS JARE</t>
-  </si>
-  <si>
-    <t>DIEGO GIOVANI</t>
-  </si>
-  <si>
-    <t>MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL FERNANDO</t>
-  </si>
-  <si>
-    <t>MARCO DIDIEL</t>
-  </si>
-  <si>
-    <t>CESAR GUADALUPE</t>
-  </si>
-  <si>
     <t>VICTOR ALEJANDRO</t>
   </si>
   <si>
@@ -485,61 +335,16 @@
     <t>SANTIAGO ZURIEL</t>
   </si>
   <si>
-    <t>KEVIN URIEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
     <t>ANGEL BRYAN</t>
   </si>
   <si>
-    <t>ELIAN RAMON</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>ALESSANDRO CALEB</t>
-  </si>
-  <si>
-    <t>CARLOS ALEXANDER</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
     <t>IVANNA GUADALUPE</t>
   </si>
   <si>
-    <t>JESUS ANDRES</t>
-  </si>
-  <si>
     <t>DAVID</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>CRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>ADBIEL</t>
-  </si>
-  <si>
-    <t>ISA ANGELICA</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>JUAN ALEXIS</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +866,7 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -1085,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -1133,7 +938,7 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -1162,7 +967,7 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1186,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>8</v>
@@ -1234,7 +1039,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1263,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1287,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -1335,7 +1140,7 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1364,7 +1169,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1388,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1436,7 +1241,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1465,7 +1270,7 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6.2</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1489,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1537,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1566,7 +1371,7 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1590,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1638,7 +1443,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1667,7 +1472,7 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6.8</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -1691,7 +1496,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -1739,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1768,7 +1573,7 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1792,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -1840,7 +1645,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1869,7 +1674,7 @@
         <v>22</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>8.5</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1893,7 +1698,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -1941,7 +1746,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1970,7 +1775,7 @@
         <v>23</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1994,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -2042,7 +1847,7 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -2071,7 +1876,7 @@
         <v>24</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -2095,7 +1900,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -2143,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -2172,7 +1977,7 @@
         <v>25</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -2196,7 +2001,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>6</v>
@@ -2244,7 +2049,7 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -2273,7 +2078,7 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -2297,7 +2102,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -2345,7 +2150,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -2374,7 +2179,7 @@
         <v>27</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7.7</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -2398,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -2446,7 +2251,7 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2475,7 +2280,7 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6.8</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2499,7 +2304,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>8</v>
@@ -2547,7 +2352,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2576,7 +2381,7 @@
         <v>29</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7.3</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2600,7 +2405,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -2648,7 +2453,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2677,7 +2482,7 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5.3</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2701,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>5</v>
@@ -2749,7 +2554,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2778,7 +2583,7 @@
         <v>31</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -2802,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -2850,7 +2655,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -2879,7 +2684,7 @@
         <v>32</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2903,7 +2708,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -2951,7 +2756,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -2980,7 +2785,7 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6.3</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -3004,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -3052,7 +2857,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -3081,7 +2886,7 @@
         <v>34</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6.8</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -3105,7 +2910,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -3153,7 +2958,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>7</v>
@@ -3182,7 +2987,7 @@
         <v>35</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -3206,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -3254,7 +3059,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -3283,7 +3088,7 @@
         <v>36</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6.2</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -3307,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -3355,7 +3160,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>5</v>
@@ -3384,7 +3189,7 @@
         <v>37</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -3408,7 +3213,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>8</v>
@@ -3456,7 +3261,7 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3485,7 +3290,7 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>4.8</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -3509,7 +3314,7 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -3557,7 +3362,7 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -3586,7 +3391,7 @@
         <v>39</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -3610,7 +3415,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -3658,7 +3463,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3687,7 +3492,7 @@
         <v>40</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -3711,7 +3516,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -3759,7 +3564,7 @@
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3788,7 +3593,7 @@
         <v>41</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -3812,7 +3617,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -3860,7 +3665,7 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>6</v>
@@ -3889,7 +3694,7 @@
         <v>42</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -3913,7 +3718,7 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>8</v>
@@ -3961,7 +3766,7 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -3990,7 +3795,7 @@
         <v>43</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -4014,7 +3819,7 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>5</v>
@@ -4062,7 +3867,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>5</v>
@@ -4091,7 +3896,7 @@
         <v>44</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C34">
         <v>6</v>
@@ -4115,7 +3920,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>8</v>
@@ -4163,7 +3968,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -4192,7 +3997,7 @@
         <v>45</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -4216,7 +4021,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>5</v>
@@ -4264,7 +4069,7 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>5</v>
@@ -4293,7 +4098,7 @@
         <v>46</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -4317,7 +4122,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>7</v>
@@ -4365,7 +4170,7 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA36">
         <v>6</v>
@@ -4394,7 +4199,7 @@
         <v>47</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5.2</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -4418,7 +4223,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>7</v>
@@ -4466,7 +4271,7 @@
         <v>-1</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>6</v>
@@ -4495,7 +4300,7 @@
         <v>48</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>7.5</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -4519,7 +4324,7 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>6</v>
@@ -4567,7 +4372,7 @@
         <v>-1</v>
       </c>
       <c r="Z38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA38">
         <v>6</v>
@@ -4596,7 +4401,7 @@
         <v>49</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>6.2</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -4620,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -4668,7 +4473,7 @@
         <v>-1</v>
       </c>
       <c r="Z39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA39">
         <v>5</v>
@@ -4697,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -4721,7 +4526,7 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
         <v>6</v>
@@ -4769,7 +4574,7 @@
         <v>-1</v>
       </c>
       <c r="Z40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA40">
         <v>6</v>
@@ -4798,7 +4603,7 @@
         <v>51</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>7.8</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -4822,7 +4627,7 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K41">
         <v>8</v>
@@ -4870,7 +4675,7 @@
         <v>-1</v>
       </c>
       <c r="Z41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA41">
         <v>7</v>
@@ -4899,7 +4704,7 @@
         <v>52</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -4923,7 +4728,7 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
         <v>7</v>
@@ -4971,7 +4776,7 @@
         <v>-1</v>
       </c>
       <c r="Z42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA42">
         <v>7</v>
@@ -5000,7 +4805,7 @@
         <v>53</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -5024,7 +4829,7 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
         <v>7</v>
@@ -5072,7 +4877,7 @@
         <v>-1</v>
       </c>
       <c r="Z43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA43">
         <v>7</v>
@@ -5101,7 +4906,7 @@
         <v>54</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>7.8</v>
       </c>
       <c r="C44">
         <v>6</v>
@@ -5125,7 +4930,7 @@
         <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
         <v>8</v>
@@ -5173,7 +4978,7 @@
         <v>-1</v>
       </c>
       <c r="Z44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA44">
         <v>7</v>
@@ -5336,7 +5141,7 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -5360,7 +5165,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -5384,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -5413,7 +5218,7 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -5437,7 +5242,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -5461,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -5490,7 +5295,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -5514,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -5538,7 +5343,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -5567,7 +5372,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>80</v>
@@ -5591,7 +5396,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K7">
         <v>83.3</v>
@@ -5615,7 +5420,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S7">
         <v>83.3</v>
@@ -5644,7 +5449,7 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C8">
         <v>93.3</v>
@@ -5668,7 +5473,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K8">
         <v>86.7</v>
@@ -5692,7 +5497,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S8">
         <v>86.7</v>
@@ -5721,7 +5526,7 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>93.3</v>
@@ -5745,7 +5550,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>96.7</v>
@@ -5769,7 +5574,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
         <v>96.7</v>
@@ -5798,7 +5603,7 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -5822,7 +5627,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>93.3</v>
@@ -5846,7 +5651,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
         <v>93.3</v>
@@ -5952,7 +5757,7 @@
         <v>22</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -5976,7 +5781,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -6000,7 +5805,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -6029,7 +5834,7 @@
         <v>23</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -6053,7 +5858,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -6077,7 +5882,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -6106,7 +5911,7 @@
         <v>24</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>86.7</v>
@@ -6130,7 +5935,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K14">
         <v>93.3</v>
@@ -6154,7 +5959,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S14">
         <v>93.3</v>
@@ -6183,7 +5988,7 @@
         <v>25</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -6207,7 +6012,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -6231,7 +6036,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -6260,7 +6065,7 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -6284,7 +6089,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>93.3</v>
@@ -6308,7 +6113,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
         <v>93.3</v>
@@ -6337,7 +6142,7 @@
         <v>27</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -6361,7 +6166,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -6385,7 +6190,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -6414,7 +6219,7 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>86.7</v>
@@ -6438,7 +6243,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>93.3</v>
@@ -6462,7 +6267,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
         <v>93.3</v>
@@ -6491,7 +6296,7 @@
         <v>29</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -6515,7 +6320,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -6539,7 +6344,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -6568,7 +6373,7 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>93.3</v>
@@ -6592,7 +6397,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K20">
         <v>90</v>
@@ -6616,7 +6421,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S20">
         <v>90</v>
@@ -6645,7 +6450,7 @@
         <v>31</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -6669,7 +6474,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -6693,7 +6498,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -6722,7 +6527,7 @@
         <v>32</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -6746,7 +6551,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>93.3</v>
@@ -6770,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
         <v>93.3</v>
@@ -6799,7 +6604,7 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -6823,7 +6628,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K23">
         <v>93.3</v>
@@ -6847,7 +6652,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S23">
         <v>93.3</v>
@@ -6876,7 +6681,7 @@
         <v>34</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -6900,7 +6705,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -6924,7 +6729,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -6953,7 +6758,7 @@
         <v>35</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -6977,7 +6782,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -7001,7 +6806,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -7030,7 +6835,7 @@
         <v>36</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -7054,7 +6859,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -7078,7 +6883,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -7107,7 +6912,7 @@
         <v>37</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -7131,7 +6936,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -7155,7 +6960,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -7184,7 +6989,7 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C28">
         <v>80</v>
@@ -7208,7 +7013,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K28">
         <v>80</v>
@@ -7232,7 +7037,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S28">
         <v>80</v>
@@ -7261,7 +7066,7 @@
         <v>39</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -7285,7 +7090,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K29">
         <v>96.7</v>
@@ -7309,7 +7114,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S29">
         <v>96.7</v>
@@ -7338,7 +7143,7 @@
         <v>40</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -7362,7 +7167,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -7386,7 +7191,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -7415,7 +7220,7 @@
         <v>41</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -7439,7 +7244,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -7463,7 +7268,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -7492,7 +7297,7 @@
         <v>42</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -7516,7 +7321,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -7540,7 +7345,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -7569,7 +7374,7 @@
         <v>43</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C33">
         <v>86.7</v>
@@ -7593,7 +7398,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K33">
         <v>83.3</v>
@@ -7617,7 +7422,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S33">
         <v>83.3</v>
@@ -7646,7 +7451,7 @@
         <v>44</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -7670,7 +7475,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -7694,7 +7499,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -7723,7 +7528,7 @@
         <v>45</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -7747,7 +7552,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -7771,7 +7576,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -7800,7 +7605,7 @@
         <v>46</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C36">
         <v>80</v>
@@ -7824,7 +7629,7 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K36">
         <v>86.7</v>
@@ -7848,7 +7653,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S36">
         <v>86.7</v>
@@ -7877,7 +7682,7 @@
         <v>47</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -7901,7 +7706,7 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -7925,7 +7730,7 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -7954,7 +7759,7 @@
         <v>48</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7978,7 +7783,7 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -8002,7 +7807,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -8031,7 +7836,7 @@
         <v>49</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -8055,7 +7860,7 @@
         <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K39">
         <v>96.7</v>
@@ -8079,7 +7884,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S39">
         <v>96.7</v>
@@ -8108,7 +7913,7 @@
         <v>50</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -8132,7 +7937,7 @@
         <v>100</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -8156,7 +7961,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -8185,7 +7990,7 @@
         <v>51</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -8209,7 +8014,7 @@
         <v>100</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -8233,7 +8038,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -8262,7 +8067,7 @@
         <v>52</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -8286,7 +8091,7 @@
         <v>100</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -8310,7 +8115,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -8339,7 +8144,7 @@
         <v>53</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -8363,7 +8168,7 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K43">
         <v>100</v>
@@ -8387,7 +8192,7 @@
         <v>100</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S43">
         <v>100</v>
@@ -8416,7 +8221,7 @@
         <v>54</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -8440,7 +8245,7 @@
         <v>100</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -8464,7 +8269,7 @@
         <v>100</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44">
         <v>100</v>
@@ -8542,7 +8347,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -8551,27 +8356,30 @@
         <v>41</v>
       </c>
       <c r="D2">
+        <v>31</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>24.4</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>41</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -8592,7 +8400,7 @@
         <v>24.4</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8603,7 +8411,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -8612,19 +8420,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>75.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2">
-        <v>24.4</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8635,7 +8443,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -8644,19 +8452,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>78</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8667,7 +8475,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -8676,19 +8484,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>82.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>17.1</v>
+        <v>14.6</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8699,7 +8507,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -8708,19 +8516,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>85.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="G7" s="2">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8731,7 +8539,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
@@ -8752,7 +8560,7 @@
         <v>12.2</v>
       </c>
       <c r="H8">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8763,7 +8571,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
@@ -8772,19 +8580,19 @@
         <v>41</v>
       </c>
       <c r="D9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2">
-        <v>87.8</v>
+        <v>90.2</v>
       </c>
       <c r="G9" s="2">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8800,7 +8608,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8827,826 +8635,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>24330051920070</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>24330051920063</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>24330051920337</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>24330051920336</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>24330051920074</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>24330051920340</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>24330051920077</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>24330051920073</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>24330051920067</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>24330051920082</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>24330051920338</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>24330051920268</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>24330051920080</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>24330051920339</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>24330051920064</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>24330051920069</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>24330051920036</v>
-      </c>
-      <c r="B18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>24330051920404</v>
-      </c>
-      <c r="B19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>24330051920066</v>
-      </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>24330051920334</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>24330051920109</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>24330051920111</v>
-      </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>24330051920076</v>
-      </c>
-      <c r="B24" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>24330051920333</v>
-      </c>
-      <c r="B25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>24330051920062</v>
-      </c>
-      <c r="B26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>24330051920332</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>24330051920314</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>24330051920034</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>24330051920079</v>
-      </c>
-      <c r="B30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>24330051920331</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>24330051920083</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>163</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>24330051920068</v>
-      </c>
-      <c r="B33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" t="s">
-        <v>164</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>24330051920065</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>24330051920299</v>
-      </c>
-      <c r="B35" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35" t="s">
-        <v>166</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>24330051920335</v>
-      </c>
-      <c r="B36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" t="s">
-        <v>167</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>24330051920071</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>24330051920084</v>
-      </c>
-      <c r="B38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D38" t="s">
-        <v>169</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>24330051920081</v>
-      </c>
-      <c r="B39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" t="s">
-        <v>170</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>24330051920075</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>24330051920072</v>
-      </c>
-      <c r="B41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>24330051920078</v>
-      </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" t="s">
-        <v>173</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>67</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9654,7 +8642,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9686,45 +8674,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920063</v>
+        <v>24330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>67</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920063</v>
+        <v>24330051920336</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -9732,45 +8720,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920337</v>
+        <v>24330051920071</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920337</v>
+        <v>24330051920071</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -9778,42 +8766,42 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920334</v>
+        <v>24330051920063</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920334</v>
+        <v>24330051920337</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>68</v>
@@ -9824,25 +8812,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920109</v>
+        <v>24330051920334</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -9850,19 +8838,19 @@
         <v>24330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -9873,42 +8861,42 @@
         <v>24330051920111</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920111</v>
+        <v>24330051920062</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -9916,45 +8904,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920062</v>
+        <v>24330051920314</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920062</v>
+        <v>24330051920068</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -9962,623 +8950,25 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920314</v>
+        <v>24330051920299</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920314</v>
-      </c>
-      <c r="B15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920068</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920068</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920299</v>
-      </c>
-      <c r="B18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920299</v>
-      </c>
-      <c r="B19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920070</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920074</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920077</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920067</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920082</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>24330051920268</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" t="s">
-        <v>144</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920080</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920339</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>24330051920064</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>24330051920069</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>24330051920036</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>24330051920066</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>24330051920076</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>24330051920034</v>
-      </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>24330051920079</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>24330051920083</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>24330051920084</v>
-      </c>
-      <c r="B36" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>24330051920081</v>
-      </c>
-      <c r="B37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" t="s">
-        <v>170</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>24330051920075</v>
-      </c>
-      <c r="B38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>24330051920072</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>24330051920078</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>67</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -257,6 +257,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -269,18 +281,21 @@
     <t>PERALTA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CHICUELLAR</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ISLAS</t>
   </si>
   <si>
@@ -291,6 +306,18 @@
   </si>
   <si>
     <t>MORALES</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ELIAN RAMON</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
   </si>
   <si>
     <t>VERONICA ITZEL</t>
@@ -7705,7 +7732,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7737,16 +7764,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920336</v>
+        <v>24330051920338</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7760,22 +7787,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920336</v>
+        <v>24330051920338</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7783,22 +7810,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920340</v>
+        <v>24330051920338</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7806,16 +7833,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920340</v>
+        <v>24330051920332</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -7829,22 +7856,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920334</v>
+        <v>24330051920332</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7852,16 +7879,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920111</v>
+        <v>24330051920332</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7875,22 +7902,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920299</v>
+        <v>24330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7898,24 +7925,300 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>24330051920065</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920065</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920335</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920335</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920335</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920336</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920336</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920340</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920340</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920334</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920299</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
         <v>24330051920071</v>
       </c>
-      <c r="B9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
         <v>67</v>
       </c>
-      <c r="G9">
+      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -224,24 +224,24 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Loyo Sanchez Raul Manuel</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Loyo Sanchez Raul Manuel</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -257,6 +257,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -269,9 +275,6 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -284,6 +287,12 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -293,9 +302,6 @@
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>ISLAS</t>
   </si>
   <si>
@@ -308,6 +314,12 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>MARCO DIDIEL</t>
+  </si>
+  <si>
+    <t>VERONICA ITZEL</t>
+  </si>
+  <si>
     <t>JONATHAN</t>
   </si>
   <si>
@@ -318,9 +330,6 @@
   </si>
   <si>
     <t>JAVIER</t>
-  </si>
-  <si>
-    <t>VERONICA ITZEL</t>
   </si>
   <si>
     <t>ANGEL ALBERTO</t>
@@ -841,7 +850,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -889,7 +898,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -904,13 +913,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>8</v>
@@ -930,7 +939,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -978,7 +987,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -993,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1019,7 +1028,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1067,7 +1076,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1156,7 +1165,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1177,7 +1186,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1197,7 +1206,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1245,7 +1254,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1266,7 +1275,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>6</v>
@@ -1286,7 +1295,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1334,7 +1343,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1349,13 +1358,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1375,7 +1384,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -1423,7 +1432,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1438,13 +1447,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1512,7 +1521,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1553,7 +1562,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1601,7 +1610,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1616,7 +1625,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1642,7 +1651,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1690,7 +1699,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1705,7 +1714,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1779,7 +1788,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1800,7 +1809,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1820,7 +1829,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1868,7 +1877,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1889,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -1957,7 +1966,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1978,7 +1987,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -1998,7 +2007,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -2046,7 +2055,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2061,13 +2070,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2087,7 +2096,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2135,7 +2144,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2176,7 +2185,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2224,7 +2233,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2265,7 +2274,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2313,7 +2322,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2334,7 +2343,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2402,7 +2411,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2423,7 +2432,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>10</v>
@@ -2443,7 +2452,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2470,7 +2479,7 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2491,7 +2500,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2506,13 +2515,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2532,7 +2541,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -2580,7 +2589,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2601,7 +2610,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>8</v>
@@ -2621,7 +2630,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2669,7 +2678,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2710,7 +2719,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2758,7 +2767,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2779,7 +2788,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2799,7 +2808,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2847,7 +2856,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2888,7 +2897,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -2936,7 +2945,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2951,7 +2960,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2977,7 +2986,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -3025,7 +3034,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3114,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3203,7 +3212,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3224,7 +3233,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>5</v>
@@ -3292,7 +3301,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3333,7 +3342,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -3381,7 +3390,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3470,7 +3479,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3511,7 +3520,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>6</v>
@@ -3559,7 +3568,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3648,7 +3657,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3669,7 +3678,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z35">
         <v>5</v>
@@ -3737,7 +3746,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3778,7 +3787,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -3826,7 +3835,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3847,7 +3856,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z37">
         <v>5</v>
@@ -3867,7 +3876,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -3915,7 +3924,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3956,7 +3965,7 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -4004,7 +4013,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -4025,7 +4034,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z39">
         <v>7</v>
@@ -4045,7 +4054,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -4093,7 +4102,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -4108,13 +4117,13 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>6</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z40">
         <v>6</v>
@@ -4134,7 +4143,7 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -4182,7 +4191,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -4197,7 +4206,7 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -4271,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -4292,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z42">
         <v>10</v>
@@ -4360,7 +4369,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4401,7 +4410,7 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="C44">
         <v>6</v>
@@ -4449,7 +4458,7 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -4464,7 +4473,7 @@
         <v>-1</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X44">
         <v>7</v>
@@ -4728,7 +4737,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4864,7 +4873,7 @@
         <v>83.3</v>
       </c>
       <c r="R7">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4932,7 +4941,7 @@
         <v>86.7</v>
       </c>
       <c r="R8">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -5068,7 +5077,7 @@
         <v>93.3</v>
       </c>
       <c r="R10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -5136,7 +5145,7 @@
         <v>50</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5612,7 +5621,7 @@
         <v>93.3</v>
       </c>
       <c r="R18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5816,7 +5825,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -6292,7 +6301,7 @@
         <v>80</v>
       </c>
       <c r="R28">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -6496,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6632,7 +6641,7 @@
         <v>83.3</v>
       </c>
       <c r="R33">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6768,7 +6777,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6836,7 +6845,7 @@
         <v>86.7</v>
       </c>
       <c r="R36">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6904,7 +6913,7 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -7040,7 +7049,7 @@
         <v>96.7</v>
       </c>
       <c r="R39">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -7108,7 +7117,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -7244,7 +7253,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -7481,7 +7490,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -7490,19 +7499,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>78</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7513,7 +7522,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -7522,19 +7531,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>82.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>17.1</v>
+        <v>14.6</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7545,7 +7554,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -7554,19 +7563,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>85.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="G5" s="2">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7577,7 +7586,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -7598,7 +7607,7 @@
         <v>12.2</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7609,7 +7618,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -7618,19 +7627,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>87.8</v>
+        <v>90.2</v>
       </c>
       <c r="G7" s="2">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7641,7 +7650,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
@@ -7650,19 +7659,19 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>90.2</v>
+        <v>92.7</v>
       </c>
       <c r="G8" s="2">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7732,7 +7741,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7764,22 +7773,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920338</v>
+        <v>24330051920404</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7787,22 +7796,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920338</v>
+        <v>24330051920404</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7810,22 +7819,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920338</v>
+        <v>24330051920404</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7833,22 +7842,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920332</v>
+        <v>24330051920404</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7856,22 +7865,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920332</v>
+        <v>24330051920336</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7879,22 +7888,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920332</v>
+        <v>24330051920336</v>
       </c>
       <c r="B7" t="s">
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7902,16 +7911,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920065</v>
+        <v>24330051920338</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -7925,22 +7934,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920065</v>
+        <v>24330051920338</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7948,22 +7957,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920065</v>
+        <v>24330051920332</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7971,22 +7980,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920335</v>
+        <v>24330051920332</v>
       </c>
       <c r="B11" t="s">
         <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7994,22 +8003,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920335</v>
+        <v>24330051920065</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8017,22 +8026,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920335</v>
+        <v>24330051920065</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8040,22 +8049,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920336</v>
+        <v>24330051920335</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8063,22 +8072,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920336</v>
+        <v>24330051920335</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8089,13 +8098,13 @@
         <v>24330051920340</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -8109,22 +8118,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920340</v>
+        <v>24330051920334</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8132,22 +8141,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920334</v>
+        <v>24330051920111</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -8155,22 +8164,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920111</v>
+        <v>24330051920299</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -8178,47 +8187,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920299</v>
+        <v>24330051920071</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920071</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -233,15 +233,15 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Loyo Sanchez Raul Manuel</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Loyo Sanchez Raul Manuel</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -260,21 +260,21 @@
     <t>PARADA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -290,18 +290,18 @@
     <t>SANTOS</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CHICUELLAR</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CHICUELLAR</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>ISLAS</t>
   </si>
   <si>
@@ -317,19 +317,19 @@
     <t>MARCO DIDIEL</t>
   </si>
   <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ELIAN RAMON</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
     <t>VERONICA ITZEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ELIAN RAMON</t>
-  </si>
-  <si>
-    <t>JESUS ANDRES</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
   </si>
   <si>
     <t>ANGEL ALBERTO</t>
@@ -904,7 +904,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -993,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1014,7 +1014,7 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>8</v>
@@ -1082,7 +1082,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1103,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1171,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1260,7 +1260,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1281,7 +1281,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>7</v>
@@ -1349,7 +1349,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1438,7 +1438,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1527,7 +1527,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1616,7 +1616,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1705,7 +1705,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1794,7 +1794,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1815,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>6</v>
@@ -1883,7 +1883,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1972,7 +1972,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1993,7 +1993,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2061,7 +2061,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2150,7 +2150,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2260,7 +2260,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2328,7 +2328,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2349,7 +2349,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB20">
         <v>7</v>
@@ -2417,7 +2417,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2506,7 +2506,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2527,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>6</v>
@@ -2595,7 +2595,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2616,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2684,7 +2684,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2773,7 +2773,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2794,7 +2794,7 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>7</v>
@@ -2862,7 +2862,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2951,7 +2951,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2972,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>8</v>
@@ -3040,7 +3040,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3061,7 +3061,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3129,7 +3129,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3150,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>6</v>
@@ -3218,7 +3218,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3307,7 +3307,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3396,7 +3396,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3506,7 +3506,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>5</v>
@@ -3574,7 +3574,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3663,7 +3663,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3684,7 +3684,7 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB35">
         <v>6</v>
@@ -3752,7 +3752,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3841,7 +3841,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3930,7 +3930,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3951,7 +3951,7 @@
         <v>10</v>
       </c>
       <c r="AA38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>7</v>
@@ -4019,7 +4019,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -4108,7 +4108,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -4197,7 +4197,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>-1</v>
@@ -4218,7 +4218,7 @@
         <v>9</v>
       </c>
       <c r="AA41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB41">
         <v>7</v>
@@ -4286,7 +4286,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U42">
         <v>-1</v>
@@ -4375,7 +4375,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U43">
         <v>-1</v>
@@ -4464,7 +4464,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>-1</v>
@@ -4485,7 +4485,7 @@
         <v>10</v>
       </c>
       <c r="AA44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB44">
         <v>7</v>
@@ -4947,7 +4947,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -5151,7 +5151,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>37.5</v>
+        <v>23.4</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -6307,7 +6307,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -6375,7 +6375,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -7586,7 +7586,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -7595,19 +7595,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>87.8</v>
+        <v>90.2</v>
       </c>
       <c r="G6" s="2">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7618,7 +7618,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -7627,16 +7627,16 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>90.2</v>
+        <v>92.7</v>
       </c>
       <c r="G7" s="2">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H7">
         <v>7.7</v>
@@ -7650,7 +7650,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
@@ -7659,19 +7659,19 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>92.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7741,7 +7741,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7788,7 +7788,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920404</v>
+        <v>24330051920338</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920336</v>
+        <v>24330051920338</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
@@ -7877,10 +7877,10 @@
         <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7888,22 +7888,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920336</v>
+        <v>24330051920332</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7911,7 +7911,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920338</v>
+        <v>24330051920332</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
@@ -7923,10 +7923,10 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7934,22 +7934,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920338</v>
+        <v>24330051920065</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7957,13 +7957,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920332</v>
+        <v>24330051920065</v>
       </c>
       <c r="B10" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
         <v>101</v>
@@ -7980,22 +7980,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920332</v>
+        <v>24330051920335</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8003,22 +8003,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920065</v>
+        <v>24330051920335</v>
       </c>
       <c r="B12" t="s">
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
         <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8026,22 +8026,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920065</v>
+        <v>24330051920336</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8049,22 +8049,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920335</v>
+        <v>24330051920340</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8072,22 +8072,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920335</v>
+        <v>24330051920334</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8095,22 +8095,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920340</v>
+        <v>24330051920111</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -8118,22 +8118,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920334</v>
+        <v>24330051920299</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8141,70 +8141,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920111</v>
+        <v>24330051920071</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920299</v>
-      </c>
-      <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920071</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20241.xlsx
+++ b/grupos/1BM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -221,27 +221,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
+    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -257,94 +257,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>PARADA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>CHICUELLAR</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>TRONCO</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MARCO DIDIEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
     <t>ELIAN RAMON</t>
-  </si>
-  <si>
-    <t>JESUS ANDRES</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>VERONICA ITZEL</t>
-  </si>
-  <si>
-    <t>ANGEL ALBERTO</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO</t>
-  </si>
-  <si>
-    <t>SANTIAGO ZURIEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>CRISTIAN YAIR</t>
   </si>
 </sst>
 </file>
@@ -892,37 +811,37 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -981,25 +900,25 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1017,10 +936,10 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1070,31 +989,31 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1106,7 +1025,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1159,31 +1078,31 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1248,31 +1167,31 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1287,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1337,25 +1256,25 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1373,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1426,25 +1345,25 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1456,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1515,25 +1434,25 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1604,31 +1523,31 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1640,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1693,25 +1612,25 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1782,31 +1701,31 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1821,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1871,37 +1790,37 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1910,7 +1829,7 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1960,25 +1879,25 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1996,7 +1915,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -2049,31 +1968,31 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2085,10 +2004,10 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2138,25 +2057,25 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2174,7 +2093,7 @@
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2227,31 +2146,31 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2263,10 +2182,10 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2316,43 +2235,43 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2405,28 +2324,28 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2494,25 +2413,25 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2524,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -2533,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2583,31 +2502,31 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2619,7 +2538,7 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2672,31 +2591,31 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2708,10 +2627,10 @@
         <v>7</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2761,25 +2680,25 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2791,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2850,43 +2769,43 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2939,25 +2858,25 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2978,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3028,28 +2947,28 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -3117,28 +3036,28 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -3153,10 +3072,10 @@
         <v>7</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3206,25 +3125,25 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3236,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3245,7 +3164,7 @@
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3295,43 +3214,43 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA31">
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -3384,25 +3303,25 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3423,7 +3342,7 @@
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3473,28 +3392,28 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3562,31 +3481,31 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>9</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3651,37 +3570,37 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>6</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>6</v>
@@ -3690,7 +3609,7 @@
         <v>6</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3740,43 +3659,43 @@
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>7</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36">
         <v>6</v>
       </c>
       <c r="AB36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC36">
         <v>7</v>
@@ -3829,46 +3748,46 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>6</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>7</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3918,43 +3837,43 @@
         <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>8</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>8</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA38">
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>8</v>
@@ -4007,43 +3926,43 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>7</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <v>7</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>7</v>
@@ -4096,31 +4015,31 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
         <v>6</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>8</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -4132,7 +4051,7 @@
         <v>6</v>
       </c>
       <c r="AB40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC40">
         <v>9</v>
@@ -4185,28 +4104,28 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -4215,13 +4134,13 @@
         <v>9</v>
       </c>
       <c r="Z41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA41">
         <v>6</v>
       </c>
       <c r="AB41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC41">
         <v>10</v>
@@ -4274,31 +4193,31 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>10</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W42">
         <v>9</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y42">
         <v>9</v>
@@ -4310,7 +4229,7 @@
         <v>8</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>10</v>
@@ -4363,28 +4282,28 @@
         <v>6</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>7</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T43">
         <v>8</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -4452,31 +4371,31 @@
         <v>9</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>10</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T44">
         <v>5</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W44">
         <v>9</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y44">
         <v>10</v>
@@ -4488,7 +4407,7 @@
         <v>6</v>
       </c>
       <c r="AB44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC44">
         <v>9</v>
@@ -4681,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4749,7 +4668,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4870,7 +4789,7 @@
         <v>80</v>
       </c>
       <c r="Q7">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R7">
         <v>90.59999999999999</v>
@@ -4885,7 +4804,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4935,10 +4854,10 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P8">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q8">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R8">
         <v>93.8</v>
@@ -4953,7 +4872,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -5006,7 +4925,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -5021,7 +4940,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -5074,7 +4993,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R10">
         <v>96.90000000000001</v>
@@ -5089,7 +5008,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5142,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="R11">
         <v>68.8</v>
@@ -5157,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="V11">
-        <v>38.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5343,10 +5262,10 @@
         <v>95.5</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q14">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -5361,7 +5280,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5429,7 +5348,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5479,10 +5398,10 @@
         <v>95.5</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q16">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5497,7 +5416,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5547,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5565,7 +5484,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5618,7 +5537,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R18">
         <v>96.90000000000001</v>
@@ -5633,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5751,10 +5670,10 @@
         <v>97.7</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -5769,7 +5688,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5819,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5837,7 +5756,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5887,10 +5806,10 @@
         <v>95.5</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q22">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5905,7 +5824,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5955,10 +5874,10 @@
         <v>95.5</v>
       </c>
       <c r="P23">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q23">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5973,7 +5892,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -6041,7 +5960,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6109,7 +6028,7 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6162,7 +6081,7 @@
         <v>90</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -6177,7 +6096,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6298,7 +6217,7 @@
         <v>80</v>
       </c>
       <c r="Q28">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="R28">
         <v>85.90000000000001</v>
@@ -6313,7 +6232,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6363,10 +6282,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q29">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -6381,7 +6300,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6431,10 +6350,10 @@
         <v>95.5</v>
       </c>
       <c r="P30">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -6449,7 +6368,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6517,7 +6436,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6585,7 +6504,7 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6638,7 +6557,7 @@
         <v>80</v>
       </c>
       <c r="Q33">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="R33">
         <v>96.90000000000001</v>
@@ -6653,7 +6572,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>88.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6771,10 +6690,10 @@
         <v>95.5</v>
       </c>
       <c r="P35">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R35">
         <v>90.59999999999999</v>
@@ -6789,7 +6708,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6842,7 +6761,7 @@
         <v>90</v>
       </c>
       <c r="Q36">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R36">
         <v>93.8</v>
@@ -6857,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="V36">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6907,10 +6826,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P37">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R37">
         <v>93.8</v>
@@ -6925,7 +6844,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6993,7 +6912,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -7043,10 +6962,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P39">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q39">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R39">
         <v>96.90000000000001</v>
@@ -7061,7 +6980,7 @@
         <v>100</v>
       </c>
       <c r="V39">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7129,7 +7048,7 @@
         <v>100</v>
       </c>
       <c r="V40">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7179,7 +7098,7 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -7250,7 +7169,7 @@
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R42">
         <v>96.90000000000001</v>
@@ -7315,7 +7234,7 @@
         <v>93.2</v>
       </c>
       <c r="P43">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q43">
         <v>100</v>
@@ -7333,7 +7252,7 @@
         <v>100</v>
       </c>
       <c r="V43">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -7386,7 +7305,7 @@
         <v>100</v>
       </c>
       <c r="Q44">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R44">
         <v>100</v>
@@ -7458,7 +7377,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -7467,19 +7386,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>75.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="G2" s="2">
-        <v>24.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7490,7 +7409,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -7499,19 +7418,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>82.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="G3" s="2">
-        <v>17.1</v>
+        <v>7.3</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7522,7 +7441,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -7531,19 +7450,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>85.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="G4" s="2">
-        <v>14.6</v>
+        <v>7.3</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7563,19 +7482,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>87.8</v>
+        <v>92.7</v>
       </c>
       <c r="G5" s="2">
-        <v>12.2</v>
+        <v>7.3</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7586,7 +7505,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -7595,19 +7514,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>90.2</v>
+        <v>92.7</v>
       </c>
       <c r="G6" s="2">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7618,7 +7537,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -7627,19 +7546,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7650,7 +7569,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
@@ -7671,7 +7590,7 @@
         <v>2.4</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7741,7 +7660,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7773,392 +7692,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920404</v>
+        <v>24330051920332</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>24330051920404</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>24330051920404</v>
-      </c>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920338</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920338</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920332</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920332</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920065</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920065</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920335</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920335</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920336</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920340</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920334</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920299</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920071</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>
